--- a/make_table/jd_self/b2.xlsx
+++ b/make_table/jd_self/b2.xlsx
@@ -520,16 +520,16 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R2" s="3" t="n">
         <v>0.0</v>
@@ -642,16 +642,16 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="O3" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="R3" s="3" t="n">
         <v>0.0</v>
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0.0</v>
